--- a/data/trans_dic/P19C05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C05-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,93; 30,61</t>
+          <t>23,83; 30,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,44; 31,1</t>
+          <t>24,52; 31,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,38; 25,06</t>
+          <t>17,31; 24,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,48; 21,36</t>
+          <t>15,21; 21,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 32,78</t>
+          <t>26,76; 32,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,35; 36,09</t>
+          <t>30,46; 36,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 24,75</t>
+          <t>18,15; 25,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,24; 29,12</t>
+          <t>24,21; 28,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,66; 31,1</t>
+          <t>26,44; 30,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,95; 33,43</t>
+          <t>28,98; 33,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,85; 23,68</t>
+          <t>18,77; 23,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,46; 25,2</t>
+          <t>21,52; 25,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 9,2</t>
+          <t>6,12; 9,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,04; 12,36</t>
+          <t>9,07; 12,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,34; 10,14</t>
+          <t>7,44; 10,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,53</t>
+          <t>5,61; 9,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 10,01</t>
+          <t>7,05; 10,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 11,93</t>
+          <t>8,71; 12,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,9; 10,96</t>
+          <t>7,86; 10,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,39</t>
+          <t>5,33; 8,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,93; 9,09</t>
+          <t>7,0; 9,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,46; 11,62</t>
+          <t>9,43; 11,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,06; 10,04</t>
+          <t>8,02; 10,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,66</t>
+          <t>6,02; 8,61</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 14,16</t>
+          <t>8,23; 14,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,96; 12,08</t>
+          <t>6,38; 12,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 10,46</t>
+          <t>5,54; 10,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 10,88</t>
+          <t>6,53; 10,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 12,71</t>
+          <t>6,96; 12,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 10,63</t>
+          <t>5,31; 11,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,84</t>
+          <t>5,17; 10,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,92</t>
+          <t>5,54; 8,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,2; 12,38</t>
+          <t>8,22; 12,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,39</t>
+          <t>6,34; 10,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,41</t>
+          <t>5,86; 9,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 9,22</t>
+          <t>6,46; 9,11</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,29; 14,88</t>
+          <t>12,36; 15,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,58; 16,38</t>
+          <t>13,65; 16,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 11,93</t>
+          <t>9,4; 11,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,75</t>
+          <t>7,33; 10,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 17,67</t>
+          <t>14,82; 17,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,79; 19,55</t>
+          <t>16,79; 19,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,52; 12,97</t>
+          <t>10,32; 12,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 12,27</t>
+          <t>8,99; 12,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,04; 16,0</t>
+          <t>13,99; 15,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,66; 17,69</t>
+          <t>15,63; 17,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,34; 12,12</t>
+          <t>10,38; 11,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,88; 11,27</t>
+          <t>9,1; 11,22</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>164945; 210983</t>
+          <t>164265; 211343</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>190452; 242291</t>
+          <t>191049; 244100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79493; 114617</t>
+          <t>79158; 112546</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74977; 103488</t>
+          <t>73700; 103162</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>256011; 314394</t>
+          <t>256618; 314125</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>342391; 407210</t>
+          <t>343652; 409415</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>115069; 158134</t>
+          <t>115987; 161226</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>174932; 210128</t>
+          <t>174688; 208354</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>439366; 512559</t>
+          <t>435867; 508540</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>552168; 637722</t>
+          <t>552764; 639250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>206607; 259607</t>
+          <t>205764; 257585</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>258847; 303967</t>
+          <t>259499; 305983</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80339; 120952</t>
+          <t>80424; 119789</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>152585; 208741</t>
+          <t>153179; 209815</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124511; 171956</t>
+          <t>126203; 176513</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>122633; 212657</t>
+          <t>125185; 214412</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94003; 137484</t>
+          <t>96770; 138881</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>141119; 189673</t>
+          <t>138529; 192729</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>135002; 187248</t>
+          <t>134255; 182943</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>110294; 184438</t>
+          <t>117176; 185678</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>186235; 244240</t>
+          <t>188206; 245696</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>310110; 380919</t>
+          <t>309177; 382364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>274339; 342004</t>
+          <t>273097; 342782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>266655; 383722</t>
+          <t>266503; 381115</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>36275; 63862</t>
+          <t>37091; 64079</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26369; 53409</t>
+          <t>28197; 54817</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27713; 52221</t>
+          <t>27675; 52184</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41555; 68705</t>
+          <t>41217; 67485</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28559; 51943</t>
+          <t>28449; 52656</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21683; 45047</t>
+          <t>22498; 46979</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25141; 49995</t>
+          <t>26285; 50861</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34989; 58136</t>
+          <t>36108; 58375</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70458; 106397</t>
+          <t>70680; 108108</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55473; 89942</t>
+          <t>54879; 90142</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58418; 94768</t>
+          <t>59085; 93138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84377; 118313</t>
+          <t>82926; 116922</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>301710; 365333</t>
+          <t>303299; 369199</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>395029; 476711</t>
+          <t>397286; 478207</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>253895; 316582</t>
+          <t>249293; 316620</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>244908; 359581</t>
+          <t>245278; 358702</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>404636; 484194</t>
+          <t>406123; 483010</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>527466; 614199</t>
+          <t>527717; 615638</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>300560; 370441</t>
+          <t>294814; 366904</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>323327; 438024</t>
+          <t>321164; 435450</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>729461; 831117</t>
+          <t>726894; 827500</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>947588; 1070673</t>
+          <t>946072; 1073643</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>569396; 667737</t>
+          <t>571697; 660194</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>614301; 779422</t>
+          <t>629800; 776165</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C05-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C05-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,83; 30,66</t>
+          <t>23,83; 30,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,52; 31,33</t>
+          <t>24,58; 31,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,31; 24,6</t>
+          <t>17,54; 25,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,21; 21,3</t>
+          <t>14,97; 20,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,76; 32,76</t>
+          <t>27,13; 32,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,46; 36,29</t>
+          <t>30,44; 36,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 25,24</t>
+          <t>18,05; 24,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,21; 28,87</t>
+          <t>24,01; 28,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,44; 30,85</t>
+          <t>26,71; 31,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,98; 33,51</t>
+          <t>28,82; 33,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,77; 23,5</t>
+          <t>18,61; 23,7</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,52; 25,37</t>
+          <t>21,11; 24,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,11</t>
+          <t>6,12; 9,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,07; 12,43</t>
+          <t>8,97; 12,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 10,4</t>
+          <t>7,43; 10,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,61; 9,61</t>
+          <t>8,09; 10,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,11</t>
+          <t>6,97; 9,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 12,12</t>
+          <t>8,88; 12,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 10,71</t>
+          <t>8,05; 11,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,45</t>
+          <t>7,45; 9,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 9,14</t>
+          <t>6,89; 9,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,43; 11,66</t>
+          <t>9,52; 11,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,02; 10,07</t>
+          <t>8,05; 10,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,61</t>
+          <t>8,13; 9,7</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 14,21</t>
+          <t>8,12; 14,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,38; 12,4</t>
+          <t>6,23; 12,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 10,45</t>
+          <t>5,58; 10,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 10,69</t>
+          <t>6,53; 10,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 12,88</t>
+          <t>6,94; 12,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,09</t>
+          <t>5,41; 10,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 10,01</t>
+          <t>5,0; 9,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 8,96</t>
+          <t>5,42; 8,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,22; 12,57</t>
+          <t>8,15; 12,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,41</t>
+          <t>6,48; 10,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,24</t>
+          <t>5,8; 9,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 9,11</t>
+          <t>6,45; 9,04</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,36; 15,04</t>
+          <t>12,22; 15,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,65; 16,44</t>
+          <t>13,58; 16,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 11,93</t>
+          <t>9,4; 11,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 10,72</t>
+          <t>9,36; 11,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 17,62</t>
+          <t>14,73; 17,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,79; 19,59</t>
+          <t>16,83; 19,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,32; 12,85</t>
+          <t>10,48; 13,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,99; 12,19</t>
+          <t>11,19; 12,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,99; 15,93</t>
+          <t>13,91; 15,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,63; 17,74</t>
+          <t>15,74; 17,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 11,98</t>
+          <t>10,27; 12,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,1; 11,22</t>
+          <t>10,61; 11,89</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88146</t>
+          <t>94715</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>192740</t>
+          <t>207437</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>280886</t>
+          <t>302151</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>164265; 211343</t>
+          <t>164302; 209305</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>191049; 244100</t>
+          <t>191504; 243434</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>79158; 112546</t>
+          <t>80236; 114814</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73700; 103162</t>
+          <t>80415; 110409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>256618; 314125</t>
+          <t>260185; 315471</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>343652; 409415</t>
+          <t>343405; 408778</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>115987; 161226</t>
+          <t>115346; 158361</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>174688; 208354</t>
+          <t>188378; 224475</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>435867; 508540</t>
+          <t>440322; 511929</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>552764; 639250</t>
+          <t>549765; 634091</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>205764; 257585</t>
+          <t>204054; 259857</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>259499; 305983</t>
+          <t>278983; 326726</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178123</t>
+          <t>198635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>157193</t>
+          <t>177991</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>335315</t>
+          <t>376626</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>80424; 119789</t>
+          <t>80389; 119417</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>153179; 209815</t>
+          <t>151510; 205886</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>126203; 176513</t>
+          <t>125997; 172700</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125185; 214412</t>
+          <t>173714; 227733</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>96770; 138881</t>
+          <t>95706; 136416</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>138529; 192729</t>
+          <t>141140; 192405</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>134255; 182943</t>
+          <t>137544; 188440</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>117176; 185678</t>
+          <t>157238; 199685</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>188206; 245696</t>
+          <t>185297; 243997</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>309177; 382364</t>
+          <t>311970; 379553</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>273097; 342782</t>
+          <t>273991; 342087</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>266503; 381115</t>
+          <t>346027; 413145</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53726</t>
+          <t>58322</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>46177</t>
+          <t>50052</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99903</t>
+          <t>108373</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>37091; 64079</t>
+          <t>36609; 63366</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28197; 54817</t>
+          <t>27544; 55736</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27675; 52184</t>
+          <t>27865; 52425</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41217; 67485</t>
+          <t>45857; 73106</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>28449; 52656</t>
+          <t>28370; 52228</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22498; 46979</t>
+          <t>22937; 45034</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26285; 50861</t>
+          <t>25397; 50764</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36108; 58375</t>
+          <t>39281; 62822</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>70680; 108108</t>
+          <t>70103; 106502</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54879; 90142</t>
+          <t>56137; 92574</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59085; 93138</t>
+          <t>58413; 92892</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82926; 116922</t>
+          <t>91979; 128897</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>319995</t>
+          <t>351671</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>396109</t>
+          <t>435479</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>716104</t>
+          <t>787150</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>303299; 369199</t>
+          <t>299928; 369344</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>397286; 478207</t>
+          <t>395061; 472351</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>249293; 316620</t>
+          <t>249353; 315889</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>245278; 358702</t>
+          <t>316972; 387497</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>406123; 483010</t>
+          <t>403825; 477766</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>527717; 615638</t>
+          <t>528982; 617833</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>294814; 366904</t>
+          <t>299287; 371840</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>321164; 435450</t>
+          <t>404999; 469508</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>726894; 827500</t>
+          <t>722756; 825630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>946072; 1073643</t>
+          <t>952290; 1072190</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>571697; 660194</t>
+          <t>565874; 667983</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>629800; 776165</t>
+          <t>743519; 832958</t>
         </is>
       </c>
     </row>
